--- a/excel/Profitus.xlsx
+++ b/excel/Profitus.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C8E8EC9-83B3-46EB-9FA9-70EF283EA400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB36775F-E26F-4D33-BD71-CBE6747D04AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="96">
   <si>
     <t>Paskola</t>
   </si>
@@ -339,6 +339,12 @@
   <si>
     <t>Realus</t>
   </si>
+  <si>
+    <t>Paskola P00001480</t>
+  </si>
+  <si>
+    <t>Investuota, Eur</t>
+  </si>
 </sst>
 </file>
 
@@ -567,22 +573,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2509,36 +2515,36 @@
       <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="34" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="O1" s="34" t="s">
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="O1" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34" t="s">
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="T1" s="34"/>
-      <c r="U1" s="35" t="s">
+      <c r="T1" s="32"/>
+      <c r="U1" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
+      <c r="V1" s="33"/>
+      <c r="W1" s="33"/>
+      <c r="X1" s="33"/>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -2704,7 +2710,7 @@
       </c>
       <c r="X3" s="13">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>8.5210481286048884E-2</v>
+        <v>8.4797057509422305E-2</v>
       </c>
       <c r="AC3" s="10" t="str">
         <f ca="1">'Ocean 11 South, II'!AA2</f>
@@ -3205,7 +3211,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!B13</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!S3</f>
@@ -3262,7 +3268,7 @@
       </c>
       <c r="J13" s="10">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!B13</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K13" s="10" t="str">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!S3</f>
@@ -3315,11 +3321,11 @@
       </c>
       <c r="I14" s="18" t="str">
         <f>'Dvibutis Didžiojoje Riešėje'!R3</f>
-        <v/>
+        <v>Investuota, Eur</v>
       </c>
       <c r="J14" s="10">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!B13</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!S3</f>
@@ -3376,7 +3382,7 @@
       </c>
       <c r="J15" s="10">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!B13</f>
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="K15" s="10" t="str">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!S3</f>
@@ -3433,7 +3439,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Golf Hills Vilos, Alikantė'!B13</f>
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Golf Hills Vilos, Alikantė'!S3</f>
@@ -3490,7 +3496,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!B13</f>
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!S3</f>
@@ -3546,7 +3552,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Brivibas 28, Jūrmala'!B13</f>
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!S3</f>
@@ -3603,7 +3609,7 @@
       </c>
       <c r="J19" s="10">
         <f ca="1">'Europos 70, Kaunas XX'!B13</f>
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K19" s="10" t="str">
         <f ca="1">'Europos 70, Kaunas XX'!S3</f>
@@ -3660,7 +3666,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Molėtų Oazė XII'!B13</f>
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Molėtų Oazė XII'!S3</f>
@@ -3717,7 +3723,7 @@
       </c>
       <c r="J21" s="10">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="K21" s="10" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
@@ -3932,18 +3938,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -4000,9 +4006,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46003</v>
@@ -4068,9 +4074,8 @@
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
         <v/>
       </c>
-      <c r="R3" s="11" t="str">
-        <f>IF(M3=N3,B14,"")</f>
-        <v/>
+      <c r="R3" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
@@ -4288,7 +4293,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>116.3</v>
@@ -4346,7 +4351,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -5078,18 +5083,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -5146,9 +5151,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45926</v>
@@ -5442,7 +5447,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>101.9</v>
@@ -5500,7 +5505,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -6232,18 +6237,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -6300,9 +6305,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45908</v>
@@ -6596,7 +6601,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>116.6</v>
@@ -6654,7 +6659,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -7391,18 +7396,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -7459,9 +7464,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45898</v>
@@ -7777,7 +7782,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>103.7</v>
@@ -8572,18 +8577,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -8640,9 +8645,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45854</v>
@@ -8944,7 +8949,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>110.5</v>
@@ -9739,18 +9744,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -9807,9 +9812,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45798</v>
@@ -10125,7 +10130,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -10912,18 +10917,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -10980,9 +10985,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45790</v>
@@ -11284,7 +11289,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -12079,18 +12084,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -12147,9 +12152,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45771</v>
@@ -12479,7 +12484,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -13274,18 +13279,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -13342,9 +13347,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45730</v>
@@ -13646,7 +13651,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="3">
         <v>100</v>
@@ -14441,18 +14446,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -14509,9 +14514,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45728</v>
@@ -14813,7 +14818,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -15596,7 +15601,7 @@
       </c>
       <c r="L1" s="13">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>8.5210481286048884E-2</v>
+        <v>8.4797057509422305E-2</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -17128,7 +17133,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -17198,18 +17203,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -17266,9 +17271,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45714</v>
@@ -17570,7 +17575,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -18364,18 +18369,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -18432,9 +18437,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45702</v>
@@ -18736,7 +18741,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>100</v>
@@ -19528,18 +19533,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -19588,9 +19593,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46164</v>
@@ -19868,7 +19873,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>102.9</v>
@@ -19926,7 +19931,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -20658,18 +20663,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -20718,9 +20723,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46156</v>
@@ -20998,7 +21003,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>105.2</v>
@@ -21056,7 +21061,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -21788,18 +21793,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -21848,9 +21853,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46139</v>
@@ -22128,7 +22133,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>120.3</v>
@@ -22186,7 +22191,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -22918,18 +22923,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -22986,9 +22991,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46101</v>
@@ -23312,7 +23317,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>135.69999999999999</v>
@@ -23382,7 +23387,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D13" s="11">
         <v>46470</v>
@@ -24119,18 +24124,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -24187,9 +24192,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46073</v>
@@ -24467,7 +24472,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>101.5</v>
@@ -24525,7 +24530,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -25228,7 +25233,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>13</v>
@@ -25257,18 +25262,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -25325,9 +25330,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46059</v>
@@ -25605,7 +25610,7 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="B11" s="5">
         <v>102.9</v>
@@ -25663,7 +25668,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -26395,18 +26400,18 @@
       <c r="M1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="N1" s="30"/>
+      <c r="N1" s="31"/>
       <c r="O1" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="31" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="31" t="s">
+      <c r="R1" s="34" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="31" t="s">
+      <c r="S1" s="34" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -26463,9 +26468,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
-      <c r="S2" s="32"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46028</v>
@@ -26801,7 +26806,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>

--- a/excel/Profitus.xlsx
+++ b/excel/Profitus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB36775F-E26F-4D33-BD71-CBE6747D04AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838B28A5-FAED-4A9D-BA46-4EBB1B385605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="13" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="X3" s="13">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>8.4797057509422305E-2</v>
+        <v>8.4387615323066725E-2</v>
       </c>
       <c r="AC3" s="10" t="str">
         <f ca="1">'Ocean 11 South, II'!AA2</f>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!B13</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!S3</f>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J13" s="10">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!B13</f>
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K13" s="10" t="str">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!S3</f>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="J14" s="10">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!B13</f>
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!S3</f>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="J15" s="10">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!B13</f>
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="K15" s="10" t="str">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!S3</f>
@@ -3439,7 +3439,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Golf Hills Vilos, Alikantė'!B13</f>
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Golf Hills Vilos, Alikantė'!S3</f>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!B13</f>
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!S3</f>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Brivibas 28, Jūrmala'!B13</f>
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!S3</f>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="J19" s="10">
         <f ca="1">'Europos 70, Kaunas XX'!B13</f>
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="K19" s="10" t="str">
         <f ca="1">'Europos 70, Kaunas XX'!S3</f>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Molėtų Oazė XII'!B13</f>
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Molėtų Oazė XII'!S3</f>
@@ -3723,7 +3723,7 @@
       </c>
       <c r="J21" s="10">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K21" s="10" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -15601,7 +15601,7 @@
       </c>
       <c r="L1" s="13">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>8.4797057509422305E-2</v>
+        <v>8.4387615323066725E-2</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -17133,7 +17133,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -19931,7 +19931,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -22191,7 +22191,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -23387,7 +23387,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D13" s="11">
         <v>46470</v>
@@ -24530,7 +24530,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -25668,7 +25668,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -26806,7 +26806,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>

--- a/excel/Profitus.xlsx
+++ b/excel/Profitus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\evald\OneDrive\Dokumentai\portfolio-analytics\portfolio-dashboard-clean\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{838B28A5-FAED-4A9D-BA46-4EBB1B385605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D30DE8-F0A3-4899-BB44-11525EAB9C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="96">
   <si>
     <t>Paskola</t>
   </si>
@@ -496,7 +496,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -558,17 +558,14 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1146,14 +1143,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2512,39 +2509,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="O1" s="32" t="s">
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="O1" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32" t="s">
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="T1" s="32"/>
-      <c r="U1" s="33" t="s">
+      <c r="T1" s="31"/>
+      <c r="U1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="32"/>
+      <c r="X1" s="32"/>
     </row>
     <row r="2" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
@@ -2628,7 +2625,7 @@
         <f>'Ocean 11 South, II'!B4</f>
         <v>45705</v>
       </c>
-      <c r="C3" s="25" t="str">
+      <c r="C3" s="27" t="str">
         <f>'Ocean 11 South, II'!B2</f>
         <v>Ocean 11 South, II</v>
       </c>
@@ -2640,7 +2637,7 @@
         <f>'Ocean 11 South, II'!B5</f>
         <v>A</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="6">
         <f>'Ocean 11 South, II'!B10</f>
         <v>7.4999999999999997E-2</v>
       </c>
@@ -2686,7 +2683,7 @@
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>14.789999999999964</v>
+        <v>17.939999999999827</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -2694,23 +2691,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>92.19</v>
+        <v>95.340000000000018</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1122.19</v>
+        <v>1125.3399999999999</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>102.19000000000005</v>
+        <v>105.33999999999992</v>
       </c>
       <c r="W3" s="13">
         <f>(U3-O3)/O3</f>
-        <v>0.10018627450980397</v>
+        <v>0.10327450980392149</v>
       </c>
       <c r="X3" s="13">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>8.4387615323066725E-2</v>
+        <v>8.6753752827644345E-2</v>
       </c>
       <c r="AC3" s="10" t="str">
         <f ca="1">'Ocean 11 South, II'!AA2</f>
@@ -2725,7 +2722,7 @@
         <f>'Bičių slėnis XVII'!B4</f>
         <v>45717</v>
       </c>
-      <c r="C4" s="25" t="str">
+      <c r="C4" s="27" t="str">
         <f>'Bičių slėnis XVII'!B2</f>
         <v>Namų kvartalas Bičių Slėnis XVII</v>
       </c>
@@ -2737,7 +2734,7 @@
         <f>'Bičių slėnis XVII'!B5</f>
         <v>A</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="6">
         <f>'Bičių slėnis XVII'!B10</f>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -2782,7 +2779,7 @@
         <f>'Piekrasta rezidence'!B4</f>
         <v>45733</v>
       </c>
-      <c r="C5" s="25" t="str">
+      <c r="C5" s="27" t="str">
         <f>'Piekrasta rezidence'!B2</f>
         <v>Piekrasta Rezidence, Ryga</v>
       </c>
@@ -2794,7 +2791,7 @@
         <f>'Piekrasta rezidence'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="6">
         <f>'Piekrasta rezidence'!B10</f>
         <v>0.11</v>
       </c>
@@ -2839,7 +2836,7 @@
         <f>'Elfa loftai II'!B4</f>
         <v>45736</v>
       </c>
-      <c r="C6" s="25" t="str">
+      <c r="C6" s="27" t="str">
         <f>'Elfa loftai II'!B2</f>
         <v>Elfa Loftai II</v>
       </c>
@@ -2851,7 +2848,7 @@
         <f>'Elfa loftai II'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="6">
         <f>'Elfa loftai II'!B10</f>
         <v>0.09</v>
       </c>
@@ -2896,7 +2893,7 @@
         <f>'Kęstučio salos'!B4</f>
         <v>45773</v>
       </c>
-      <c r="C7" s="25" t="str">
+      <c r="C7" s="27" t="str">
         <f>'Kęstučio salos'!B2</f>
         <v>Kęstučio salos</v>
       </c>
@@ -2908,7 +2905,7 @@
         <f>'Kęstučio salos'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="6">
         <f>'Kęstučio salos'!B10</f>
         <v>8.5999999999999993E-2</v>
       </c>
@@ -2953,7 +2950,7 @@
         <f>'Twinhouse XIII'!B4</f>
         <v>45792</v>
       </c>
-      <c r="C8" s="25" t="str">
+      <c r="C8" s="27" t="str">
         <f>'Twinhouse XIII'!B2</f>
         <v>Twinhouse XIII</v>
       </c>
@@ -2965,7 +2962,7 @@
         <f>'Twinhouse XIII'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="6">
         <f>'Twinhouse XIII'!B10</f>
         <v>0.08</v>
       </c>
@@ -3010,7 +3007,7 @@
         <f>'Vyčio slėnis VIII'!B4</f>
         <v>45804</v>
       </c>
-      <c r="C9" s="25" t="str">
+      <c r="C9" s="27" t="str">
         <f>'Vyčio slėnis VIII'!B2</f>
         <v>Vyčio slėnis VIII</v>
       </c>
@@ -3022,7 +3019,7 @@
         <f>'Vyčio slėnis VIII'!B5</f>
         <v>A</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="6">
         <f>'Vyčio slėnis VIII'!B10</f>
         <v>0.09</v>
       </c>
@@ -3067,7 +3064,7 @@
         <f>'Dvibutis Upės g.'!B4</f>
         <v>45857</v>
       </c>
-      <c r="C10" s="25" t="str">
+      <c r="C10" s="27" t="str">
         <f>'Dvibutis Upės g.'!B2</f>
         <v>Dvibutis Upės g., Vilniaus r.</v>
       </c>
@@ -3079,7 +3076,7 @@
         <f>'Vyčio slėnis VIII'!B5</f>
         <v>A</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="6">
         <f>'Dvibutis Upės g.'!B10</f>
         <v>0.08</v>
       </c>
@@ -3124,7 +3121,7 @@
         <f>'Dvibutis Klevų g.'!B4</f>
         <v>45898</v>
       </c>
-      <c r="C11" s="25" t="str">
+      <c r="C11" s="27" t="str">
         <f>'Dvibutis Klevų g.'!B2</f>
         <v>Dvibutis Klevų g., Kauno r.</v>
       </c>
@@ -3136,7 +3133,7 @@
         <f>'Dvibutis Klevų g.'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="6">
         <f>'Dvibutis Klevų g.'!B10</f>
         <v>0.08</v>
       </c>
@@ -3181,7 +3178,7 @@
         <f>'Dvibutis Upelio g., Vilniaus r.'!B4</f>
         <v>45909</v>
       </c>
-      <c r="C12" s="25" t="str">
+      <c r="C12" s="27" t="str">
         <f>'Dvibutis Upelio g., Vilniaus r.'!B2</f>
         <v>Dvibutis Upelio g., Vilniaus r.</v>
       </c>
@@ -3193,11 +3190,11 @@
         <f>'Dvibutis Upelio g., Vilniaus r.'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="6">
         <f>'Dvibutis Upelio g., Vilniaus r.'!B10</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="5">
         <f>'Dvibutis Upelio g., Vilniaus r.'!B11</f>
         <v>116.6</v>
       </c>
@@ -3211,7 +3208,7 @@
       </c>
       <c r="J12" s="10">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!B13</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!S3</f>
@@ -3238,7 +3235,7 @@
         <f>'Piekrasta Rezidence, Ryga XII'!B4</f>
         <v>45926</v>
       </c>
-      <c r="C13" s="25" t="str">
+      <c r="C13" s="27" t="str">
         <f>'Piekrasta Rezidence, Ryga XII'!B2</f>
         <v>Piekrasta Rezidence, Ryga XII</v>
       </c>
@@ -3250,7 +3247,7 @@
         <f>'Piekrasta Rezidence, Ryga XII'!B5</f>
         <v>AA-</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="6">
         <f>'Piekrasta Rezidence, Ryga XII'!B10</f>
         <v>8.5000000000000006E-2</v>
       </c>
@@ -3268,7 +3265,7 @@
       </c>
       <c r="J13" s="10">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!B13</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K13" s="10" t="str">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!S3</f>
@@ -3295,7 +3292,7 @@
         <f>'Dvibutis Didžiojoje Riešėje'!B4</f>
         <v>46003</v>
       </c>
-      <c r="C14" s="25" t="str">
+      <c r="C14" s="27" t="str">
         <f>'Dvibutis Didžiojoje Riešėje'!B2</f>
         <v>Dvibutis Didžiojoje Riešėje</v>
       </c>
@@ -3307,7 +3304,7 @@
         <f>'Dvibutis Didžiojoje Riešėje'!B5</f>
         <v>A</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="6">
         <f>'Dvibutis Didžiojoje Riešėje'!B10</f>
         <v>0.09</v>
       </c>
@@ -3321,11 +3318,11 @@
       </c>
       <c r="I14" s="18" t="str">
         <f>'Dvibutis Didžiojoje Riešėje'!R3</f>
-        <v>Investuota, Eur</v>
+        <v/>
       </c>
       <c r="J14" s="10">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!B13</f>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!S3</f>
@@ -3352,7 +3349,7 @@
         <f>'Sklypas Kalnėnuose, Vilnius II'!B4</f>
         <v>46034</v>
       </c>
-      <c r="C15" s="25" t="str">
+      <c r="C15" s="27" t="str">
         <f>'Sklypas Kalnėnuose, Vilnius II'!B2</f>
         <v>Sklypas Kalnėnuose, Vilnius II</v>
       </c>
@@ -3364,7 +3361,7 @@
         <f>'Sklypas Kalnėnuose, Vilnius II'!B5</f>
         <v>AA+</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="6">
         <f>'Sklypas Kalnėnuose, Vilnius II'!B10</f>
         <v>0.08</v>
       </c>
@@ -3382,7 +3379,7 @@
       </c>
       <c r="J15" s="10">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!B13</f>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K15" s="10" t="str">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!S3</f>
@@ -3394,7 +3391,7 @@
       </c>
       <c r="M15" s="5">
         <f>'Sklypas Kalnėnuose, Vilnius II'!P3</f>
-        <v>2.44</v>
+        <v>4.54</v>
       </c>
       <c r="AC15" s="10" t="str">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!AA2</f>
@@ -3409,7 +3406,7 @@
         <f>'Golf Hills Vilos, Alikantė'!B4</f>
         <v>46062</v>
       </c>
-      <c r="C16" s="25" t="str">
+      <c r="C16" s="27" t="str">
         <f>'Golf Hills Vilos, Alikantė'!B2</f>
         <v>Golf Hills Vilos, Alikantė</v>
       </c>
@@ -3421,7 +3418,7 @@
         <f>'Golf Hills Vilos, Alikantė'!B5</f>
         <v>AA</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="6">
         <f>'Golf Hills Vilos, Alikantė'!B10</f>
         <v>9.6000000000000002E-2</v>
       </c>
@@ -3439,7 +3436,7 @@
       </c>
       <c r="J16" s="10">
         <f ca="1">'Golf Hills Vilos, Alikantė'!B13</f>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K16" s="10" t="str">
         <f ca="1">'Golf Hills Vilos, Alikantė'!S3</f>
@@ -3466,7 +3463,7 @@
         <f>'Svajonių Daugiabutis, Kaunas'!B4</f>
         <v>46076</v>
       </c>
-      <c r="C17" s="25" t="str">
+      <c r="C17" s="27" t="str">
         <f>'Svajonių Daugiabutis, Kaunas'!B2</f>
         <v>Svajonių Daugiabutis, Kaunas</v>
       </c>
@@ -3478,7 +3475,7 @@
         <f>'Svajonių Daugiabutis, Kaunas'!B5</f>
         <v>A-</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="6">
         <f>'Svajonių Daugiabutis, Kaunas'!B10</f>
         <v>0.09</v>
       </c>
@@ -3496,7 +3493,7 @@
       </c>
       <c r="J17" s="10">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!B13</f>
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!S3</f>
@@ -3523,7 +3520,7 @@
         <f>'Brivibas 28, Jūrmala'!B4</f>
         <v>46107</v>
       </c>
-      <c r="C18" s="25" t="str">
+      <c r="C18" s="27" t="str">
         <f>'Brivibas 28, Jūrmala'!B2</f>
         <v>Brivibas 28, Jūrmala</v>
       </c>
@@ -3535,7 +3532,7 @@
         <f>'Brivibas 28, Jūrmala'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="6">
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="G18" s="5">
@@ -3552,7 +3549,7 @@
       </c>
       <c r="J18" s="10">
         <f ca="1">'Brivibas 28, Jūrmala'!B13</f>
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!S3</f>
@@ -3564,7 +3561,7 @@
       </c>
       <c r="M18" s="5">
         <f>'Brivibas 28, Jūrmala'!P3</f>
-        <v>3.24</v>
+        <v>4.29</v>
       </c>
       <c r="AC18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!AA2</f>
@@ -3579,7 +3576,7 @@
         <f>'Europos 70, Kaunas XX'!B4</f>
         <v>46139</v>
       </c>
-      <c r="C19" s="25" t="str">
+      <c r="C19" s="27" t="str">
         <f>'Europos 70, Kaunas XX'!B2</f>
         <v>Europos 70, Kaunas XX</v>
       </c>
@@ -3591,7 +3588,7 @@
         <f>'Europos 70, Kaunas XX'!B5</f>
         <v>A+</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="6">
         <f>'Europos 70, Kaunas XX'!B10</f>
         <v>8.2000000000000003E-2</v>
       </c>
@@ -3609,11 +3606,11 @@
       </c>
       <c r="J19" s="10">
         <f ca="1">'Europos 70, Kaunas XX'!B13</f>
-        <v>269</v>
-      </c>
-      <c r="K19" s="10" t="str">
+        <v>268</v>
+      </c>
+      <c r="K19" s="10">
         <f ca="1">'Europos 70, Kaunas XX'!S3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L19" s="5">
         <f>'Europos 70, Kaunas XX'!N3</f>
@@ -3625,7 +3622,7 @@
       </c>
       <c r="AC19" s="10" t="str">
         <f ca="1">'Europos 70, Kaunas XX'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
@@ -3636,7 +3633,7 @@
         <f>'Molėtų Oazė XII'!B3</f>
         <v>46156</v>
       </c>
-      <c r="C20" s="26" t="str">
+      <c r="C20" s="27" t="str">
         <f>'Molėtų Oazė XII'!B2</f>
         <v>Molėtų Oazė XII</v>
       </c>
@@ -3648,7 +3645,7 @@
         <f>'Molėtų Oazė XII'!B5</f>
         <v>A-</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="6">
         <f>'Molėtų Oazė XII'!B10</f>
         <v>8.5999999999999993E-2</v>
       </c>
@@ -3666,7 +3663,7 @@
       </c>
       <c r="J20" s="10">
         <f ca="1">'Molėtų Oazė XII'!B13</f>
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Molėtų Oazė XII'!S3</f>
@@ -3693,7 +3690,7 @@
         <f>'Dvibučių kvartalas Kauno r. II'!B3</f>
         <v>46164</v>
       </c>
-      <c r="C21" s="26" t="str">
+      <c r="C21" s="27" t="str">
         <f>'Dvibučių kvartalas Kauno r. II'!B2</f>
         <v>Dvibučių kvartalas Kauno r. II</v>
       </c>
@@ -3705,7 +3702,7 @@
         <f>'Dvibučių kvartalas Kauno r. II'!B5</f>
         <v>A</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="6">
         <f>'Dvibučių kvartalas Kauno r. II'!B10</f>
         <v>0.08</v>
       </c>
@@ -3723,7 +3720,7 @@
       </c>
       <c r="J21" s="10">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K21" s="10" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
@@ -3742,10 +3739,10 @@
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="11"/>
-      <c r="C22" s="26"/>
+      <c r="C22" s="27"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="13"/>
+      <c r="F22" s="6"/>
       <c r="G22" s="5"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
@@ -3758,10 +3755,10 @@
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="11"/>
-      <c r="C23" s="26"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="13"/>
+      <c r="F23" s="6"/>
       <c r="G23" s="5"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
@@ -3774,10 +3771,10 @@
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="11"/>
-      <c r="C24" s="26"/>
+      <c r="C24" s="27"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="13"/>
+      <c r="F24" s="6"/>
       <c r="G24" s="5"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
@@ -3790,10 +3787,10 @@
     <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="11"/>
-      <c r="C25" s="26"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="13"/>
+      <c r="F25" s="6"/>
       <c r="G25" s="5"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
@@ -3806,10 +3803,10 @@
     <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="11"/>
-      <c r="C26" s="26"/>
+      <c r="C26" s="27"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="13"/>
+      <c r="F26" s="6"/>
       <c r="G26" s="5"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
@@ -3822,10 +3819,10 @@
     <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="11"/>
-      <c r="C27" s="26"/>
+      <c r="C27" s="27"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="13"/>
+      <c r="F27" s="6"/>
       <c r="G27" s="5"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
@@ -3847,18 +3844,18 @@
     <mergeCell ref="U1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="79" priority="24">
+    <cfRule type="expression" dxfId="79" priority="1">
+      <formula>$AC3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="2">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="78" priority="25">
-      <formula>#REF!="+"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="77" priority="1">
+    <cfRule type="expression" dxfId="77" priority="3">
       <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="2">
+    <cfRule type="expression" dxfId="76" priority="4">
       <formula>$AC20="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3935,21 +3932,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -4006,9 +4003,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46003</v>
@@ -4074,8 +4071,9 @@
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
         <v/>
       </c>
-      <c r="R3" s="8" t="s">
-        <v>95</v>
+      <c r="R3" s="8" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
       </c>
       <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
@@ -4351,7 +4349,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -5080,21 +5078,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -5151,9 +5149,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45926</v>
@@ -5505,7 +5503,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -6234,21 +6232,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -6305,9 +6303,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45908</v>
@@ -6659,7 +6657,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -7306,8 +7304,8 @@
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="28"/>
+      <c r="Y42" s="25"/>
+      <c r="Z42" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7393,21 +7391,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -7464,9 +7462,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45898</v>
@@ -8574,21 +8572,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -8645,9 +8643,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45854</v>
@@ -9741,21 +9739,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -9812,9 +9810,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45798</v>
@@ -10914,21 +10912,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -10985,9 +10983,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45790</v>
@@ -12081,21 +12079,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -12152,9 +12150,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45771</v>
@@ -13276,21 +13274,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -13347,9 +13345,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45730</v>
@@ -14443,21 +14441,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -14514,9 +14512,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45728</v>
@@ -15601,7 +15599,7 @@
       </c>
       <c r="L1" s="13">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>8.4387615323066725E-2</v>
+        <v>8.6753752827644345E-2</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -17133,14 +17131,14 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="23">
         <f ca="1">TODAY()</f>
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
       <c r="K200" s="24">
         <f>Overview!U3</f>
-        <v>1122.19</v>
+        <v>1125.3399999999999</v>
       </c>
     </row>
   </sheetData>
@@ -17200,21 +17198,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -17271,9 +17269,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45714</v>
@@ -18366,21 +18364,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -18437,9 +18435,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>45702</v>
@@ -19530,21 +19528,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -19593,9 +19591,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46164</v>
@@ -19931,7 +19929,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -20660,21 +20658,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -20723,9 +20721,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46156</v>
@@ -21061,7 +21059,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -21790,21 +21788,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -21853,9 +21851,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46139</v>
@@ -21866,7 +21864,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -21917,9 +21915,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -22191,7 +22189,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -22920,21 +22918,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -22991,9 +22989,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46101</v>
@@ -23053,7 +23051,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>3.24</v>
+        <v>4.29</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -23133,13 +23131,21 @@
       <c r="F5" s="5">
         <v>1.05</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="11">
+        <v>46234</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="Y5" s="11">
         <f t="shared" si="1"/>
@@ -23176,11 +23182,11 @@
       </c>
       <c r="Y6" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46234</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -23387,7 +23393,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D13" s="11">
         <v>46470</v>
@@ -24032,7 +24038,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="9"/>
-        <v>3.24</v>
+        <v>4.29</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="9"/>
@@ -24121,21 +24127,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -24192,9 +24198,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46073</v>
@@ -24530,7 +24536,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -25259,21 +25265,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -25330,9 +25336,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46059</v>
@@ -25668,7 +25674,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -26397,21 +26403,21 @@
       <c r="K1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="31"/>
-      <c r="O1" s="29" t="s">
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="S1" s="34" t="s">
+      <c r="S1" s="33" t="s">
         <v>75</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -26468,9 +26474,9 @@
       <c r="P2" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
       <c r="Y2" s="11">
         <f>B3</f>
         <v>46028</v>
@@ -26500,13 +26506,21 @@
       <c r="F3" s="5">
         <v>2.1</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46234</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M3" s="5">
         <f>B11</f>
@@ -26522,7 +26536,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.44</v>
+        <v>4.54</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -26571,11 +26585,11 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y13" si="1">J3</f>
-        <v>0</v>
+        <v>46234</v>
       </c>
       <c r="Z4" s="5">
         <f t="shared" ref="Z4:Z13" si="2">G3+H3+I3</f>
-        <v>0</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -26806,7 +26820,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -27445,7 +27459,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="7"/>
-        <v>2.44</v>
+        <v>4.54</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="7"/>

--- a/excel/Profitus.xlsx
+++ b/excel/Profitus.xlsx
@@ -5,35 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Profitus\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Profitus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D30DE8-F0A3-4899-BB44-11525EAB9C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713D3C94-3CC5-4DB3-8133-CBA49244A8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Pinigai" sheetId="12" r:id="rId2"/>
-    <sheet name="Dvibučių kvartalas Kauno r. II" sheetId="21" r:id="rId3"/>
-    <sheet name="Molėtų Oazė XII" sheetId="20" r:id="rId4"/>
-    <sheet name="Europos 70, Kaunas XX" sheetId="19" r:id="rId5"/>
-    <sheet name="Brivibas 28, Jūrmala" sheetId="18" r:id="rId6"/>
-    <sheet name="Svajonių Daugiabutis, Kaunas" sheetId="17" r:id="rId7"/>
-    <sheet name="Golf Hills Vilos, Alikantė" sheetId="16" r:id="rId8"/>
-    <sheet name="Sklypas Kalnėnuose, Vilnius II" sheetId="15" r:id="rId9"/>
-    <sheet name="Dvibutis Didžiojoje Riešėje" sheetId="14" r:id="rId10"/>
-    <sheet name="Piekrasta Rezidence, Ryga XII" sheetId="13" r:id="rId11"/>
-    <sheet name="Dvibutis Upelio g., Vilniaus r." sheetId="11" r:id="rId12"/>
-    <sheet name="Dvibutis Klevų g." sheetId="10" r:id="rId13"/>
-    <sheet name="Dvibutis Upės g." sheetId="9" r:id="rId14"/>
-    <sheet name="Vyčio slėnis VIII" sheetId="8" r:id="rId15"/>
-    <sheet name="Twinhouse XIII" sheetId="7" r:id="rId16"/>
-    <sheet name="Kęstučio salos" sheetId="6" r:id="rId17"/>
-    <sheet name="Elfa loftai II" sheetId="5" r:id="rId18"/>
-    <sheet name="Piekrasta rezidence" sheetId="4" r:id="rId19"/>
-    <sheet name="Bičių slėnis XVII" sheetId="3" r:id="rId20"/>
-    <sheet name="Ocean 11 South, II" sheetId="2" r:id="rId21"/>
+    <sheet name="Senvagės loftai, Panevėžys VIII" sheetId="22" r:id="rId3"/>
+    <sheet name="Dvibučių kvartalas Kauno r. II" sheetId="21" r:id="rId4"/>
+    <sheet name="Molėtų Oazė XII" sheetId="20" r:id="rId5"/>
+    <sheet name="Europos 70, Kaunas XX" sheetId="19" r:id="rId6"/>
+    <sheet name="Brivibas 28, Jūrmala" sheetId="18" r:id="rId7"/>
+    <sheet name="Svajonių Daugiabutis, Kaunas" sheetId="17" r:id="rId8"/>
+    <sheet name="Golf Hills Vilos, Alikantė" sheetId="16" r:id="rId9"/>
+    <sheet name="Sklypas Kalnėnuose, Vilnius II" sheetId="15" r:id="rId10"/>
+    <sheet name="Dvibutis Didžiojoje Riešėje" sheetId="14" r:id="rId11"/>
+    <sheet name="Piekrasta Rezidence, Ryga XII" sheetId="13" r:id="rId12"/>
+    <sheet name="Dvibutis Upelio g., Vilniaus r." sheetId="11" r:id="rId13"/>
+    <sheet name="Dvibutis Klevų g." sheetId="10" r:id="rId14"/>
+    <sheet name="Dvibutis Upės g." sheetId="9" r:id="rId15"/>
+    <sheet name="Vyčio slėnis VIII" sheetId="8" r:id="rId16"/>
+    <sheet name="Twinhouse XIII" sheetId="7" r:id="rId17"/>
+    <sheet name="Kęstučio salos" sheetId="6" r:id="rId18"/>
+    <sheet name="Elfa loftai II" sheetId="5" r:id="rId19"/>
+    <sheet name="Piekrasta rezidence" sheetId="4" r:id="rId20"/>
+    <sheet name="Bičių slėnis XVII" sheetId="3" r:id="rId21"/>
+    <sheet name="Ocean 11 South, II" sheetId="2" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="98">
   <si>
     <t>Paskola</t>
   </si>
@@ -345,6 +346,12 @@
   <si>
     <t>Investuota, Eur</t>
   </si>
+  <si>
+    <t>Senvagės loftai, Panevėžys VIII</t>
+  </si>
+  <si>
+    <t>Paskola  P00001423-8</t>
+  </si>
 </sst>
 </file>
 
@@ -593,7 +600,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="80">
+  <dxfs count="84">
     <dxf>
       <fill>
         <patternFill>
@@ -1136,6 +1143,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -1168,6 +1203,622 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5E7923C-56B9-46D9-BBF8-D20C51F409E4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD4B838-9BF9-4ECA-B07A-2BFFC2C168CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93679FCB-138C-434B-B390-3FF89405D357}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A37030-8B84-4809-9B4D-C8218EAE11F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C1DD46-664C-4F71-8A67-675DC84F5392}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A05BE88-446E-440D-8ED2-ED9EB303E3D6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Graphic 5" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11345721-C595-4535-A6CC-1547978DE677}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E388F2DF-1A2D-470D-BB98-2706D50F664A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21112D91-162F-4511-820D-4110B6F7E038}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E3E8E8-4656-4C7C-AF4E-5401EF118AC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECDCECD-FD0E-4AC6-B040-FB442B89662A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1223,511 +1874,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93679FCB-138C-434B-B390-3FF89405D357}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A37030-8B84-4809-9B4D-C8218EAE11F7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8C1DD46-664C-4F71-8A67-675DC84F5392}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A05BE88-446E-440D-8ED2-ED9EB303E3D6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Graphic 5" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{11345721-C595-4535-A6CC-1547978DE677}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E388F2DF-1A2D-470D-BB98-2706D50F664A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{21112D91-162F-4511-820D-4110B6F7E038}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56E3E8E8-4656-4C7C-AF4E-5401EF118AC1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Graphic 2" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BECDCECD-FD0E-4AC6-B040-FB442B89662A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1783,7 +1930,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1839,7 +1986,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1895,7 +2042,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1951,7 +2098,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2007,7 +2154,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2063,7 +2210,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2119,7 +2266,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2141,62 +2288,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E378D716-4BFE-491D-807D-1B088876F5E9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="3619500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AD4B838-9BF9-4ECA-B07A-2BFFC2C168CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2645,11 +2736,11 @@
         <f>'Ocean 11 South, II'!B11</f>
         <v>100</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="11">
         <f>'Ocean 11 South, II'!B12</f>
         <v>46068</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I3" s="11">
         <f>'Ocean 11 South, II'!R3</f>
         <v>46073</v>
       </c>
@@ -2671,19 +2762,19 @@
       </c>
       <c r="O3" s="5">
         <f>Pinigai!I2</f>
-        <v>1020</v>
+        <v>1114.17</v>
       </c>
       <c r="P3" s="5">
         <f>SUM(G3:G200)-S3</f>
-        <v>1107.4000000000001</v>
+        <v>1229.5000000000002</v>
       </c>
       <c r="Q3" s="5">
         <f>Pinigai!H2</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R3" s="5">
         <f>U3-P3</f>
-        <v>17.939999999999827</v>
+        <v>11.2199999999998</v>
       </c>
       <c r="S3" s="5">
         <f>SUM(L3:L200)</f>
@@ -2691,23 +2782,23 @@
       </c>
       <c r="T3" s="5">
         <f>SUM(M3:M200)</f>
-        <v>95.340000000000018</v>
+        <v>106.55000000000001</v>
       </c>
       <c r="U3" s="5">
         <f>O3+T3+Q3</f>
-        <v>1125.3399999999999</v>
+        <v>1240.72</v>
       </c>
       <c r="V3" s="5">
         <f>U3-O3</f>
-        <v>105.33999999999992</v>
+        <v>126.54999999999995</v>
       </c>
       <c r="W3" s="13">
         <f>(U3-O3)/O3</f>
-        <v>0.10327450980392149</v>
+        <v>0.11358230790633382</v>
       </c>
       <c r="X3" s="13">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>8.6753752827644345E-2</v>
+        <v>9.6519476175308233E-2</v>
       </c>
       <c r="AC3" s="10" t="str">
         <f ca="1">'Ocean 11 South, II'!AA2</f>
@@ -2742,11 +2833,11 @@
         <f>'Bičių slėnis XVII'!B11</f>
         <v>100</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="11">
         <f>'Bičių slėnis XVII'!B12</f>
         <v>46080</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="11">
         <f>'Bičių slėnis XVII'!R3</f>
         <v>45925</v>
       </c>
@@ -2799,11 +2890,11 @@
         <f>'Piekrasta rezidence'!B11</f>
         <v>100</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="11">
         <f>'Piekrasta rezidence'!B12</f>
         <v>46098</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="11">
         <f>'Piekrasta rezidence'!R3</f>
         <v>46101</v>
       </c>
@@ -2856,11 +2947,11 @@
         <f>'Elfa loftai II'!B11</f>
         <v>100</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="11">
         <f>'Elfa loftai II'!B12</f>
         <v>45918</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="11">
         <f>'Elfa loftai II'!R3</f>
         <v>45898</v>
       </c>
@@ -2913,11 +3004,11 @@
         <f>'Kęstučio salos'!B11</f>
         <v>100</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="11">
         <f>'Kęstučio salos'!B12</f>
         <v>46136</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="11">
         <f>'Kęstučio salos'!R3</f>
         <v>46162</v>
       </c>
@@ -2970,11 +3061,11 @@
         <f>'Twinhouse XIII'!B11</f>
         <v>100</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="11">
         <f>'Twinhouse XIII'!B12</f>
         <v>46155</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="11">
         <f>'Twinhouse XIII'!R3</f>
         <v>46156</v>
       </c>
@@ -3027,11 +3118,11 @@
         <f>'Vyčio slėnis VIII'!B11</f>
         <v>100</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="11">
         <f>'Vyčio slėnis VIII'!B12</f>
         <v>46167</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="11">
         <f>'Vyčio slėnis VIII'!R3</f>
         <v>46077</v>
       </c>
@@ -3084,11 +3175,11 @@
         <f>'Dvibutis Upės g.'!B11</f>
         <v>110.5</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="11">
         <f>'Dvibutis Upės g.'!B12</f>
         <v>46220</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="11">
         <f>'Dvibutis Upės g.'!R3</f>
         <v>46139</v>
       </c>
@@ -3141,11 +3232,11 @@
         <f>'Dvibutis Klevų g.'!B11</f>
         <v>103.7</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="11">
         <f>'Dvibutis Klevų g.'!B12</f>
         <v>46262</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="11">
         <f>'Dvibutis Klevų g.'!R3</f>
         <v>46093</v>
       </c>
@@ -3198,17 +3289,17 @@
         <f>'Dvibutis Upelio g., Vilniaus r.'!B11</f>
         <v>116.6</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="11">
         <f>'Dvibutis Upelio g., Vilniaus r.'!B12</f>
         <v>46272</v>
       </c>
-      <c r="I12" s="18" t="str">
+      <c r="I12" s="11" t="str">
         <f>'Dvibutis Upelio g., Vilniaus r.'!R3</f>
         <v/>
       </c>
       <c r="J12" s="10">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!B13</f>
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="K12" s="10" t="str">
         <f ca="1">'Dvibutis Upelio g., Vilniaus r.'!S3</f>
@@ -3255,17 +3346,17 @@
         <f>'Piekrasta Rezidence, Ryga XII'!B11</f>
         <v>101.9</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="11">
         <f>'Piekrasta Rezidence, Ryga XII'!B12</f>
         <v>46290</v>
       </c>
-      <c r="I13" s="18" t="str">
+      <c r="I13" s="11" t="str">
         <f>'Piekrasta Rezidence, Ryga XII'!R3</f>
         <v/>
       </c>
       <c r="J13" s="10">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!B13</f>
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="K13" s="10" t="str">
         <f ca="1">'Piekrasta Rezidence, Ryga XII'!S3</f>
@@ -3312,17 +3403,17 @@
         <f>'Dvibutis Didžiojoje Riešėje'!B11</f>
         <v>116.3</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="11">
         <f>'Dvibutis Didžiojoje Riešėje'!B12</f>
         <v>46367</v>
       </c>
-      <c r="I14" s="18" t="str">
+      <c r="I14" s="11" t="str">
         <f>'Dvibutis Didžiojoje Riešėje'!R3</f>
         <v/>
       </c>
       <c r="J14" s="10">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!B13</f>
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="K14" s="10" t="str">
         <f ca="1">'Dvibutis Didžiojoje Riešėje'!S3</f>
@@ -3369,17 +3460,17 @@
         <f>'Sklypas Kalnėnuose, Vilnius II'!B11</f>
         <v>104.1</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="11">
         <f>'Sklypas Kalnėnuose, Vilnius II'!B12</f>
         <v>46398</v>
       </c>
-      <c r="I15" s="18" t="str">
+      <c r="I15" s="11" t="str">
         <f>'Sklypas Kalnėnuose, Vilnius II'!R3</f>
         <v/>
       </c>
       <c r="J15" s="10">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!B13</f>
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="K15" s="10" t="str">
         <f ca="1">'Sklypas Kalnėnuose, Vilnius II'!S3</f>
@@ -3426,21 +3517,21 @@
         <f>'Golf Hills Vilos, Alikantė'!B11</f>
         <v>102.9</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="11">
         <f>'Golf Hills Vilos, Alikantė'!B12</f>
         <v>46426</v>
       </c>
-      <c r="I16" s="18" t="str">
+      <c r="I16" s="11" t="str">
         <f>'Golf Hills Vilos, Alikantė'!R3</f>
         <v/>
       </c>
       <c r="J16" s="10">
         <f ca="1">'Golf Hills Vilos, Alikantė'!B13</f>
-        <v>191</v>
-      </c>
-      <c r="K16" s="10" t="str">
+        <v>160</v>
+      </c>
+      <c r="K16" s="10">
         <f ca="1">'Golf Hills Vilos, Alikantė'!S3</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
         <f>'Golf Hills Vilos, Alikantė'!N3</f>
@@ -3452,7 +3543,7 @@
       </c>
       <c r="AC16" s="10" t="str">
         <f ca="1">'Golf Hills Vilos, Alikantė'!AA2</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.25">
@@ -3483,17 +3574,17 @@
         <f>'Svajonių Daugiabutis, Kaunas'!B11</f>
         <v>101.5</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="11">
         <f>'Svajonių Daugiabutis, Kaunas'!B12</f>
         <v>46440</v>
       </c>
-      <c r="I17" s="18" t="str">
+      <c r="I17" s="11" t="str">
         <f>'Svajonių Daugiabutis, Kaunas'!R3</f>
         <v/>
       </c>
       <c r="J17" s="10">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!B13</f>
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="K17" s="10" t="str">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!S3</f>
@@ -3505,7 +3596,7 @@
       </c>
       <c r="M17" s="5">
         <f>'Svajonių Daugiabutis, Kaunas'!P3</f>
-        <v>2.4</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="AC17" s="10" t="str">
         <f ca="1">'Svajonių Daugiabutis, Kaunas'!AA2</f>
@@ -3539,17 +3630,17 @@
         <f>'Brivibas 28, Jūrmala'!B11</f>
         <v>135.69999999999999</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="11">
         <f>'Brivibas 28, Jūrmala'!B12</f>
         <v>46470</v>
       </c>
-      <c r="I18" s="18" t="str">
+      <c r="I18" s="11" t="str">
         <f>'Brivibas 28, Jūrmala'!R3</f>
         <v/>
       </c>
       <c r="J18" s="10">
         <f ca="1">'Brivibas 28, Jūrmala'!B13</f>
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="K18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!S3</f>
@@ -3561,7 +3652,7 @@
       </c>
       <c r="M18" s="5">
         <f>'Brivibas 28, Jūrmala'!P3</f>
-        <v>4.29</v>
+        <v>5.34</v>
       </c>
       <c r="AC18" s="10" t="str">
         <f ca="1">'Brivibas 28, Jūrmala'!AA2</f>
@@ -3596,21 +3687,21 @@
         <f>'Europos 70, Kaunas XX'!B11</f>
         <v>120.3</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="11">
         <f>'Europos 70, Kaunas XX'!B12</f>
         <v>46503</v>
       </c>
-      <c r="I19" s="18" t="str">
+      <c r="I19" s="11" t="str">
         <f>'Europos 70, Kaunas XX'!R3</f>
         <v/>
       </c>
       <c r="J19" s="10">
         <f ca="1">'Europos 70, Kaunas XX'!B13</f>
-        <v>268</v>
-      </c>
-      <c r="K19" s="10">
+        <v>237</v>
+      </c>
+      <c r="K19" s="10" t="str">
         <f ca="1">'Europos 70, Kaunas XX'!S3</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="L19" s="5">
         <f>'Europos 70, Kaunas XX'!N3</f>
@@ -3618,11 +3709,11 @@
       </c>
       <c r="M19" s="5">
         <f>'Europos 70, Kaunas XX'!P3</f>
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AC19" s="10" t="str">
         <f ca="1">'Europos 70, Kaunas XX'!AA2</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
@@ -3653,17 +3744,17 @@
         <f>'Molėtų Oazė XII'!B11</f>
         <v>105.2</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="11">
         <f>'Molėtų Oazė XII'!B12</f>
         <v>46520</v>
       </c>
-      <c r="I20" s="18" t="str">
+      <c r="I20" s="11" t="str">
         <f>'Molėtų Oazė XII'!R3</f>
         <v/>
       </c>
       <c r="J20" s="10">
         <f ca="1">'Molėtų Oazė XII'!B13</f>
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="K20" s="10" t="str">
         <f ca="1">'Molėtų Oazė XII'!S3</f>
@@ -3674,8 +3765,8 @@
         <v>0</v>
       </c>
       <c r="M20" s="5">
-        <f>'Europos 70, Kaunas XX'!P3</f>
-        <v>0</v>
+        <f>'Molėtų Oazė XII'!P3</f>
+        <v>2.68</v>
       </c>
       <c r="AC20" s="5" t="str">
         <f ca="1">'Molėtų Oazė XII'!AA2</f>
@@ -3710,17 +3801,17 @@
         <f>'Dvibučių kvartalas Kauno r. II'!B11</f>
         <v>102.9</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="11">
         <f>'Dvibučių kvartalas Kauno r. II'!B12</f>
         <v>46531</v>
       </c>
-      <c r="I21" s="18" t="str">
+      <c r="I21" s="11" t="str">
         <f>'Dvibučių kvartalas Kauno r. II'!R3</f>
         <v/>
       </c>
       <c r="J21" s="10">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!B13</f>
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="K21" s="10" t="str">
         <f ca="1">'Dvibučių kvartalas Kauno r. II'!S3</f>
@@ -3732,24 +3823,65 @@
       </c>
       <c r="M21" s="5">
         <f>'Dvibučių kvartalas Kauno r. II'!P3</f>
-        <v>0</v>
-      </c>
-      <c r="AC21" s="22"/>
+        <v>2.19</v>
+      </c>
+      <c r="AC21" s="22" t="str">
+        <f ca="1">'Dvibučių kvartalas Kauno r. II'!AA2</f>
+        <v/>
+      </c>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5"/>
+      <c r="A22" s="3">
+        <v>20</v>
+      </c>
+      <c r="B22" s="11">
+        <f>'Senvagės loftai, Panevėžys VIII'!B3</f>
+        <v>46254</v>
+      </c>
+      <c r="C22" s="27" t="str">
+        <f>'Senvagės loftai, Panevėžys VIII'!B2</f>
+        <v>Senvagės loftai, Panevėžys VIII</v>
+      </c>
+      <c r="D22" s="3">
+        <f>'Senvagės loftai, Panevėžys VIII'!B8</f>
+        <v>12</v>
+      </c>
+      <c r="E22" s="3" t="str">
+        <f>'Senvagės loftai, Panevėžys VIII'!B5</f>
+        <v>A-</v>
+      </c>
+      <c r="F22" s="6">
+        <f>'Senvagės loftai, Panevėžys VIII'!B10</f>
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="G22" s="5">
+        <f>'Senvagės loftai, Panevėžys VIII'!B11</f>
+        <v>122.1</v>
+      </c>
+      <c r="H22" s="11">
+        <f>'Senvagės loftai, Panevėžys VIII'!B12</f>
+        <v>46617</v>
+      </c>
+      <c r="I22" s="11" t="str">
+        <f>'Senvagės loftai, Panevėžys VIII'!R3</f>
+        <v/>
+      </c>
+      <c r="J22" s="10">
+        <f ca="1">'Senvagės loftai, Panevėžys VIII'!B13</f>
+        <v>351</v>
+      </c>
+      <c r="K22" s="10" t="str">
+        <f ca="1">'Senvagės loftai, Panevėžys VIII'!S3</f>
+        <v/>
+      </c>
+      <c r="L22" s="5">
+        <f>'Senvagės loftai, Panevėžys VIII'!N3</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="5">
+        <f>'Senvagės loftai, Panevėžys VIII'!P3</f>
+        <v>0</v>
+      </c>
       <c r="AC22" s="22"/>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.25">
@@ -3760,13 +3892,16 @@
       <c r="E23" s="3"/>
       <c r="F23" s="6"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5"/>
-      <c r="AC23" s="22"/>
+      <c r="AC23" s="22" t="str">
+        <f ca="1">'Senvagės loftai, Panevėžys VIII'!AA2</f>
+        <v/>
+      </c>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
@@ -3776,8 +3911,8 @@
       <c r="E24" s="3"/>
       <c r="F24" s="6"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="5"/>
@@ -3792,8 +3927,8 @@
       <c r="E25" s="3"/>
       <c r="F25" s="6"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="5"/>
@@ -3808,8 +3943,8 @@
       <c r="E26" s="3"/>
       <c r="F26" s="6"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="5"/>
@@ -3824,8 +3959,8 @@
       <c r="E27" s="3"/>
       <c r="F27" s="6"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="5"/>
@@ -3844,18 +3979,18 @@
     <mergeCell ref="U1:X1"/>
   </mergeCells>
   <conditionalFormatting sqref="A3:M27">
-    <cfRule type="expression" dxfId="79" priority="1">
+    <cfRule type="expression" dxfId="83" priority="1">
       <formula>$AC3="+"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="78" priority="2">
+    <cfRule type="expression" dxfId="82" priority="2">
       <formula>AND($G3&gt;0,$G3=$L3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC20">
-    <cfRule type="expression" dxfId="77" priority="3">
+    <cfRule type="expression" dxfId="81" priority="3">
       <formula>AND($G20&gt;0,$G20=$L20)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="4">
+    <cfRule type="expression" dxfId="80" priority="4">
       <formula>$AC20="+"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3879,6 +4014,7 @@
     <hyperlink ref="C17" location="'Svajonių Daugiabutis, Kaunas'!A1" display="'Svajonių Daugiabutis, Kaunas'!A1" xr:uid="{470DF5F1-2181-414B-BFF6-9313F2EF4D35}"/>
     <hyperlink ref="C20" location="'Molėtų Oazė XII'!A1" display="'Molėtų Oazė XII'!A1" xr:uid="{C77C31F0-859F-41C7-BB0D-077213C6BFDD}"/>
     <hyperlink ref="C21" location="'Dvibučių kvartalas Kauno r. II'!A1" display="'Dvibučių kvartalas Kauno r. II'!A1" xr:uid="{FBC5EDA2-57DE-4AA7-8E84-8F8D5A43AAB4}"/>
+    <hyperlink ref="C22" location="'Senvagės loftai, Panevėžys VIII'!A1" display="'Senvagės loftai, Panevėžys VIII'!A1" xr:uid="{6DA15196-B1F0-483C-BD6A-4B724659FA37}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3886,6 +4022,1152 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46142</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.44</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46142</v>
+      </c>
+      <c r="K2" s="10">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="Y2" s="11">
+        <f>B3</f>
+        <v>46028</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-104.1</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46028</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46234</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46234</v>
+      </c>
+      <c r="K3" s="10">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>104.1</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>8.2800000000000011</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>4.54</v>
+      </c>
+      <c r="Q3" s="13" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="11" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>46142</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46034</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46326</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2.1</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y13" si="1">J3</f>
+        <v>46234</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z13" si="2">G3+H3+I3</f>
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="11">
+        <v>46398</v>
+      </c>
+      <c r="E5" s="5">
+        <v>104.1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1.64</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5">
+        <v>104.1</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="21">
+        <v>46398</v>
+      </c>
+      <c r="D12" s="19"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="10">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>132</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" ref="Y14" si="3">J13</f>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" ref="Z14" si="4">G13+H13+I13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="11">
+        <f t="shared" ref="Y15:Y41" si="5">J14</f>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" ref="Z15:Z41" si="6">G14+H14+I14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="7"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="7"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="7"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>104.1</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="7">SUM(F2:F41)</f>
+        <v>8.2800000000000011</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="7"/>
+        <v>4.54</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="S1:S2"/>
+    <mergeCell ref="R1:R2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="51" priority="14">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="15">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="49" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="48" priority="3">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4349,7 +5631,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -5029,7 +6311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5503,7 +6785,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -6183,7 +7465,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6657,7 +7939,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -7339,7 +8621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -8520,7 +9802,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -9687,7 +10969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -10860,7 +12142,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -12027,7 +13309,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -13222,7 +14504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -14389,7 +15671,1605 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L200"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
+    <col min="2" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="12" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="13">
+        <f ca="1">XIRR(K2:K200,A2:A200)</f>
+        <v>9.6519476175308233E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
+        <v>45702</v>
+      </c>
+      <c r="B2" s="5">
+        <v>100</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <f>SUM(B2:B36)</f>
+        <v>1114.17</v>
+      </c>
+      <c r="G2" s="5">
+        <f>SUM(C2:C36)</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <f>SUM(D2:D36)</f>
+        <v>20</v>
+      </c>
+      <c r="I2" s="5">
+        <f>F2-G2</f>
+        <v>1114.17</v>
+      </c>
+      <c r="K2" s="5">
+        <f>B2*-1</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>45714</v>
+      </c>
+      <c r="B3" s="5">
+        <v>100</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5">
+        <f t="shared" ref="K3:K13" si="0">B3*-1</f>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>45728</v>
+      </c>
+      <c r="B4" s="5">
+        <v>100</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>45730</v>
+      </c>
+      <c r="B5" s="5">
+        <v>100</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>45771</v>
+      </c>
+      <c r="B6" s="5">
+        <v>100</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>45790</v>
+      </c>
+      <c r="B7" s="5">
+        <v>100</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>45798</v>
+      </c>
+      <c r="B8" s="5">
+        <v>100</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>45854</v>
+      </c>
+      <c r="B9" s="5">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>45908</v>
+      </c>
+      <c r="B10" s="5">
+        <v>100</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>10</v>
+      </c>
+      <c r="K10" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>46003</v>
+      </c>
+      <c r="B11" s="5">
+        <v>100</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>0</v>
+      </c>
+      <c r="K11" s="5">
+        <f t="shared" si="0"/>
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>46059</v>
+      </c>
+      <c r="B12" s="5">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0</v>
+      </c>
+      <c r="K12" s="5">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="11">
+        <v>46254</v>
+      </c>
+      <c r="B13" s="5">
+        <v>94.17</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>10</v>
+      </c>
+      <c r="K13" s="5">
+        <f t="shared" si="0"/>
+        <v>-94.17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="23"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="23"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="23"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="23"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="23"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="23"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="23"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="23"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="23"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="K24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="23"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="K25" s="2"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="23"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="K26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="23"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="K27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="K28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="23"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="K29" s="2"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="23"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="K30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="23"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="K31" s="2"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="23"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="23"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="23"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="K34" s="2"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="23"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="K35" s="2"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="23"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="K36" s="2"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="23"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="K37" s="2"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="23"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="K38" s="2"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="23"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="23"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="23"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="23"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="23"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="23"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="23"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="23"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="23"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="23"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="23"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="23"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="23"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="23"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="23"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="23"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="23"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="23"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="23"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="K57" s="2"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="23"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="K58" s="2"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="23"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="K59" s="2"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="23"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="23"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="K61" s="2"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="23"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+      <c r="D62" s="2"/>
+      <c r="K62" s="2"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="23"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="23"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="K64" s="2"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="23"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="K65" s="2"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="23"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="K66" s="2"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="23"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="K67" s="2"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="23"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="K68" s="2"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="23"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="2"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="23"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="23"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="23"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="23"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="23"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="23"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="23"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="23"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="23"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="K78" s="2"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="23"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="K79" s="2"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="23"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="K80" s="2"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="23"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="K81" s="2"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="23"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="K82" s="2"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="23"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="23"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="K84" s="2"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="23"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="K85" s="2"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="23"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="K86" s="2"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="23"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="K87" s="2"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="23"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="K88" s="2"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="23"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="K89" s="2"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="23"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="K90" s="2"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="23"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="23"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="K92" s="2"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="23"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="K93" s="2"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="23"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="K94" s="2"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="23"/>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
+      <c r="D95" s="2"/>
+      <c r="K95" s="2"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="23"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="K96" s="2"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="23"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="K97" s="2"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="23"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="K98" s="2"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="23"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="K99" s="2"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="23"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="K100" s="2"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="23"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="K101" s="2"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="23"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="K102" s="2"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="23"/>
+      <c r="B103" s="2"/>
+      <c r="C103" s="2"/>
+      <c r="D103" s="2"/>
+      <c r="K103" s="2"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="23"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="K104" s="2"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="23"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="K105" s="2"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="23"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="K106" s="2"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="23"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="K107" s="2"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="23"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="K108" s="2"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="23"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="K109" s="2"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="23"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="K110" s="2"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="23"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="K111" s="2"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="23"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="K112" s="2"/>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="23"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="K113" s="2"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="23"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="K114" s="2"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="23"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="K115" s="2"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="23"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="K116" s="2"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="23"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="K117" s="2"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="23"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="K118" s="2"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="23"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="K119" s="2"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="23"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="K120" s="2"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="23"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="K121" s="2"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="23"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="K122" s="2"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="23"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="K123" s="2"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="23"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="K124" s="2"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" s="23"/>
+      <c r="B125" s="2"/>
+      <c r="C125" s="2"/>
+      <c r="D125" s="2"/>
+      <c r="K125" s="2"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="23"/>
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="K126" s="2"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="23"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="K127" s="2"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="23"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="K128" s="2"/>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="23"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="K129" s="2"/>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="23"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="K130" s="2"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" s="23"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="K131" s="2"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="23"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="K132" s="2"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" s="23"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="K133" s="2"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="23"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
+      <c r="D134" s="2"/>
+      <c r="K134" s="2"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="23"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="K135" s="2"/>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" s="23"/>
+      <c r="B136" s="2"/>
+      <c r="C136" s="2"/>
+      <c r="D136" s="2"/>
+      <c r="K136" s="2"/>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="23"/>
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="K137" s="2"/>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="23"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="K138" s="2"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="23"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="K139" s="2"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="23"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="K140" s="2"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="23"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="K141" s="2"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="23"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="K142" s="2"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="23"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="K143" s="2"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" s="23"/>
+      <c r="B144" s="2"/>
+      <c r="C144" s="2"/>
+      <c r="D144" s="2"/>
+      <c r="K144" s="2"/>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="23"/>
+      <c r="B145" s="2"/>
+      <c r="C145" s="2"/>
+      <c r="D145" s="2"/>
+      <c r="K145" s="2"/>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="23"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="K146" s="2"/>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="23"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="K147" s="2"/>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" s="23"/>
+      <c r="B148" s="2"/>
+      <c r="C148" s="2"/>
+      <c r="D148" s="2"/>
+      <c r="K148" s="2"/>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="23"/>
+      <c r="B149" s="2"/>
+      <c r="C149" s="2"/>
+      <c r="D149" s="2"/>
+      <c r="K149" s="2"/>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="23"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="K150" s="2"/>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="23"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="K151" s="2"/>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="23"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="K152" s="2"/>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="23"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="K153" s="2"/>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="23"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="K154" s="2"/>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" s="23"/>
+      <c r="B155" s="2"/>
+      <c r="C155" s="2"/>
+      <c r="D155" s="2"/>
+      <c r="K155" s="2"/>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="23"/>
+      <c r="B156" s="2"/>
+      <c r="C156" s="2"/>
+      <c r="D156" s="2"/>
+      <c r="K156" s="2"/>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="23"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="K157" s="2"/>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="23"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="K158" s="2"/>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="23"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="K159" s="2"/>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="23"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="K160" s="2"/>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="23"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="K161" s="2"/>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="23"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="K162" s="2"/>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="23"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="K163" s="2"/>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="23"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="K164" s="2"/>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="23"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="K165" s="2"/>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="23"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="K166" s="2"/>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="23"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="K167" s="2"/>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" s="23"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="K168" s="2"/>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="23"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="K169" s="2"/>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="23"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="K170" s="2"/>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="23"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="K171" s="2"/>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="23"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="K172" s="2"/>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="23"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="K173" s="2"/>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="23"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="K174" s="2"/>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="23"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="K175" s="2"/>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="23"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="K176" s="2"/>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="23"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="K177" s="2"/>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="23"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="K178" s="2"/>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="23"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="K179" s="2"/>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="23"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="K180" s="2"/>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="23"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="K181" s="2"/>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="23"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="K182" s="2"/>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" s="23"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="K183" s="2"/>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="23"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="K184" s="2"/>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="23"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="K185" s="2"/>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="23"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="K186" s="2"/>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="23"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="K187" s="2"/>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="23"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="K188" s="2"/>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="23"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="K189" s="2"/>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" s="23"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="K190" s="2"/>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="23"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="K191" s="2"/>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="23"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="K192" s="2"/>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="23"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="K193" s="2"/>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="23"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="K194" s="2"/>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="23"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="K195" s="2"/>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="23"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="K196" s="2"/>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="23"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="K197" s="2"/>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" s="23"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="K198" s="2"/>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" s="23"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="K199" s="2"/>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="23">
+        <f ca="1">TODAY()</f>
+        <v>46266</v>
+      </c>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="K200" s="24">
+        <f>Overview!U3</f>
+        <v>1240.72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -15556,1597 +18436,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L200"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="15.7109375" style="12" customWidth="1"/>
-    <col min="2" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="12" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="13">
-        <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>8.6753752827644345E-2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="11">
-        <v>45702</v>
-      </c>
-      <c r="B2" s="5">
-        <v>100</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <f>SUM(B2:B36)</f>
-        <v>1020</v>
-      </c>
-      <c r="G2" s="5">
-        <f>SUM(C2:C36)</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <f>SUM(D2:D36)</f>
-        <v>10</v>
-      </c>
-      <c r="I2" s="5">
-        <f>F2-G2</f>
-        <v>1020</v>
-      </c>
-      <c r="K2" s="5">
-        <f>B2*-1</f>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="11">
-        <v>45714</v>
-      </c>
-      <c r="B3" s="5">
-        <v>100</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="K3" s="5">
-        <f t="shared" ref="K3:K13" si="0">B3*-1</f>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>45728</v>
-      </c>
-      <c r="B4" s="5">
-        <v>100</v>
-      </c>
-      <c r="C4" s="5">
-        <v>0</v>
-      </c>
-      <c r="D4" s="5">
-        <v>0</v>
-      </c>
-      <c r="K4" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="11">
-        <v>45730</v>
-      </c>
-      <c r="B5" s="5">
-        <v>100</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="11">
-        <v>45771</v>
-      </c>
-      <c r="B6" s="5">
-        <v>100</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0</v>
-      </c>
-      <c r="D6" s="5">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="11">
-        <v>45790</v>
-      </c>
-      <c r="B7" s="5">
-        <v>100</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0</v>
-      </c>
-      <c r="D7" s="5">
-        <v>0</v>
-      </c>
-      <c r="K7" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="11">
-        <v>45798</v>
-      </c>
-      <c r="B8" s="5">
-        <v>100</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0</v>
-      </c>
-      <c r="D8" s="5">
-        <v>0</v>
-      </c>
-      <c r="K8" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="11">
-        <v>45854</v>
-      </c>
-      <c r="B9" s="5">
-        <v>100</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0</v>
-      </c>
-      <c r="K9" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="11">
-        <v>45908</v>
-      </c>
-      <c r="B10" s="5">
-        <v>100</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>10</v>
-      </c>
-      <c r="K10" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="11">
-        <v>46003</v>
-      </c>
-      <c r="B11" s="5">
-        <v>100</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>0</v>
-      </c>
-      <c r="K11" s="5">
-        <f t="shared" si="0"/>
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="11">
-        <v>46059</v>
-      </c>
-      <c r="B12" s="5">
-        <v>20</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="23"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="K13" s="5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="23"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="K14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="23"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="K15" s="2"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="23"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="K16" s="2"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="23"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="K17" s="2"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="23"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="K18" s="2"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="23"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="K19" s="2"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="23"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="K20" s="2"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="23"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="K21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="K22" s="2"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="K23" s="2"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="K24" s="2"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="K25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="K26" s="2"/>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="K27" s="2"/>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="23"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="K29" s="2"/>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="K30" s="2"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="K31" s="2"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="23"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="K34" s="2"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="K35" s="2"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="23"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="K37" s="2"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="K38" s="2"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="K39" s="2"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="K40" s="2"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="23"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="K41" s="2"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="K42" s="2"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="K43" s="2"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="23"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="23"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="23"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="23"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="23"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="23"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="23"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="23"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="23"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="23"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="23"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="23"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="23"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="23"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="23"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="23"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="23"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A66" s="23"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="K66" s="2"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A67" s="23"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="K67" s="2"/>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="23"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="K68" s="2"/>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="23"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A70" s="23"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="2"/>
-      <c r="D70" s="2"/>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A71" s="23"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="2"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" s="23"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="2"/>
-      <c r="D72" s="2"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="23"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
-      <c r="D73" s="2"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="23"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="2"/>
-      <c r="D74" s="2"/>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="23"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="2"/>
-      <c r="D75" s="2"/>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="23"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A77" s="23"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A78" s="23"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="2"/>
-      <c r="D78" s="2"/>
-      <c r="K78" s="2"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="23"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="2"/>
-      <c r="D79" s="2"/>
-      <c r="K79" s="2"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80" s="23"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="2"/>
-      <c r="D80" s="2"/>
-      <c r="K80" s="2"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="23"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="2"/>
-      <c r="K81" s="2"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="23"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="2"/>
-      <c r="K82" s="2"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="23"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="2"/>
-      <c r="D83" s="2"/>
-      <c r="K83" s="2"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="23"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="2"/>
-      <c r="D84" s="2"/>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="23"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="2"/>
-      <c r="D85" s="2"/>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="23"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="2"/>
-      <c r="D86" s="2"/>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="23"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="2"/>
-      <c r="D87" s="2"/>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="23"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="2"/>
-      <c r="D88" s="2"/>
-      <c r="K88" s="2"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="23"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A90" s="23"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="K90" s="2"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="23"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="K91" s="2"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="23"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="K92" s="2"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="23"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="K93" s="2"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="23"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="K94" s="2"/>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="23"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="K95" s="2"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="23"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="K96" s="2"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="23"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="K97" s="2"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="23"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="K98" s="2"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="23"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="K99" s="2"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="23"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="K100" s="2"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="23"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="K101" s="2"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="23"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="K102" s="2"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="23"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="K103" s="2"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="23"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="K104" s="2"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="23"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="K105" s="2"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="23"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="K106" s="2"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="23"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="K107" s="2"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="23"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="K108" s="2"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="23"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="K109" s="2"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="23"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="K110" s="2"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="23"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="K111" s="2"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="23"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="K112" s="2"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A113" s="23"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="K113" s="2"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A114" s="23"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="K114" s="2"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A115" s="23"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="K115" s="2"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A116" s="23"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="K116" s="2"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A117" s="23"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="K117" s="2"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A118" s="23"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="K118" s="2"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A119" s="23"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="K119" s="2"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A120" s="23"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="K120" s="2"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A121" s="23"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="K121" s="2"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A122" s="23"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="K122" s="2"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A123" s="23"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="K123" s="2"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A124" s="23"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="K124" s="2"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A125" s="23"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="K125" s="2"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A126" s="23"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="K126" s="2"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A127" s="23"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="K127" s="2"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A128" s="23"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="K128" s="2"/>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A129" s="23"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="K129" s="2"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A130" s="23"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="K130" s="2"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A131" s="23"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="K131" s="2"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A132" s="23"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="K132" s="2"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A133" s="23"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="K133" s="2"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A134" s="23"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="K134" s="2"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A135" s="23"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="K135" s="2"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A136" s="23"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="K136" s="2"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A137" s="23"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="K137" s="2"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A138" s="23"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="K138" s="2"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A139" s="23"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="K139" s="2"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A140" s="23"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="K140" s="2"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A141" s="23"/>
-      <c r="B141" s="2"/>
-      <c r="C141" s="2"/>
-      <c r="D141" s="2"/>
-      <c r="K141" s="2"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A142" s="23"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="K142" s="2"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A143" s="23"/>
-      <c r="B143" s="2"/>
-      <c r="C143" s="2"/>
-      <c r="D143" s="2"/>
-      <c r="K143" s="2"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A144" s="23"/>
-      <c r="B144" s="2"/>
-      <c r="C144" s="2"/>
-      <c r="D144" s="2"/>
-      <c r="K144" s="2"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A145" s="23"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="K145" s="2"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A146" s="23"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="K146" s="2"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A147" s="23"/>
-      <c r="B147" s="2"/>
-      <c r="C147" s="2"/>
-      <c r="D147" s="2"/>
-      <c r="K147" s="2"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A148" s="23"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="K148" s="2"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A149" s="23"/>
-      <c r="B149" s="2"/>
-      <c r="C149" s="2"/>
-      <c r="D149" s="2"/>
-      <c r="K149" s="2"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A150" s="23"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="2"/>
-      <c r="D150" s="2"/>
-      <c r="K150" s="2"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A151" s="23"/>
-      <c r="B151" s="2"/>
-      <c r="C151" s="2"/>
-      <c r="D151" s="2"/>
-      <c r="K151" s="2"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A152" s="23"/>
-      <c r="B152" s="2"/>
-      <c r="C152" s="2"/>
-      <c r="D152" s="2"/>
-      <c r="K152" s="2"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A153" s="23"/>
-      <c r="B153" s="2"/>
-      <c r="C153" s="2"/>
-      <c r="D153" s="2"/>
-      <c r="K153" s="2"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A154" s="23"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
-      <c r="D154" s="2"/>
-      <c r="K154" s="2"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A155" s="23"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="K155" s="2"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A156" s="23"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="K156" s="2"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A157" s="23"/>
-      <c r="B157" s="2"/>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="K157" s="2"/>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A158" s="23"/>
-      <c r="B158" s="2"/>
-      <c r="C158" s="2"/>
-      <c r="D158" s="2"/>
-      <c r="K158" s="2"/>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A159" s="23"/>
-      <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
-      <c r="D159" s="2"/>
-      <c r="K159" s="2"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A160" s="23"/>
-      <c r="B160" s="2"/>
-      <c r="C160" s="2"/>
-      <c r="D160" s="2"/>
-      <c r="K160" s="2"/>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A161" s="23"/>
-      <c r="B161" s="2"/>
-      <c r="C161" s="2"/>
-      <c r="D161" s="2"/>
-      <c r="K161" s="2"/>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A162" s="23"/>
-      <c r="B162" s="2"/>
-      <c r="C162" s="2"/>
-      <c r="D162" s="2"/>
-      <c r="K162" s="2"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A163" s="23"/>
-      <c r="B163" s="2"/>
-      <c r="C163" s="2"/>
-      <c r="D163" s="2"/>
-      <c r="K163" s="2"/>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A164" s="23"/>
-      <c r="B164" s="2"/>
-      <c r="C164" s="2"/>
-      <c r="D164" s="2"/>
-      <c r="K164" s="2"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A165" s="23"/>
-      <c r="B165" s="2"/>
-      <c r="C165" s="2"/>
-      <c r="D165" s="2"/>
-      <c r="K165" s="2"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A166" s="23"/>
-      <c r="B166" s="2"/>
-      <c r="C166" s="2"/>
-      <c r="D166" s="2"/>
-      <c r="K166" s="2"/>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A167" s="23"/>
-      <c r="B167" s="2"/>
-      <c r="C167" s="2"/>
-      <c r="D167" s="2"/>
-      <c r="K167" s="2"/>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A168" s="23"/>
-      <c r="B168" s="2"/>
-      <c r="C168" s="2"/>
-      <c r="D168" s="2"/>
-      <c r="K168" s="2"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A169" s="23"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
-      <c r="D169" s="2"/>
-      <c r="K169" s="2"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A170" s="23"/>
-      <c r="B170" s="2"/>
-      <c r="C170" s="2"/>
-      <c r="D170" s="2"/>
-      <c r="K170" s="2"/>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A171" s="23"/>
-      <c r="B171" s="2"/>
-      <c r="C171" s="2"/>
-      <c r="D171" s="2"/>
-      <c r="K171" s="2"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A172" s="23"/>
-      <c r="B172" s="2"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="K172" s="2"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A173" s="23"/>
-      <c r="B173" s="2"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="K173" s="2"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A174" s="23"/>
-      <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
-      <c r="K174" s="2"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A175" s="23"/>
-      <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
-      <c r="K175" s="2"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A176" s="23"/>
-      <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="K176" s="2"/>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A177" s="23"/>
-      <c r="B177" s="2"/>
-      <c r="C177" s="2"/>
-      <c r="D177" s="2"/>
-      <c r="K177" s="2"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A178" s="23"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
-      <c r="K178" s="2"/>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A179" s="23"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
-      <c r="K179" s="2"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A180" s="23"/>
-      <c r="B180" s="2"/>
-      <c r="C180" s="2"/>
-      <c r="D180" s="2"/>
-      <c r="K180" s="2"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A181" s="23"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
-      <c r="D181" s="2"/>
-      <c r="K181" s="2"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A182" s="23"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
-      <c r="K182" s="2"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A183" s="23"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
-      <c r="K183" s="2"/>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A184" s="23"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
-      <c r="K184" s="2"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A185" s="23"/>
-      <c r="B185" s="2"/>
-      <c r="C185" s="2"/>
-      <c r="D185" s="2"/>
-      <c r="K185" s="2"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A186" s="23"/>
-      <c r="B186" s="2"/>
-      <c r="C186" s="2"/>
-      <c r="D186" s="2"/>
-      <c r="K186" s="2"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A187" s="23"/>
-      <c r="B187" s="2"/>
-      <c r="C187" s="2"/>
-      <c r="D187" s="2"/>
-      <c r="K187" s="2"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A188" s="23"/>
-      <c r="B188" s="2"/>
-      <c r="C188" s="2"/>
-      <c r="D188" s="2"/>
-      <c r="K188" s="2"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A189" s="23"/>
-      <c r="B189" s="2"/>
-      <c r="C189" s="2"/>
-      <c r="D189" s="2"/>
-      <c r="K189" s="2"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A190" s="23"/>
-      <c r="B190" s="2"/>
-      <c r="C190" s="2"/>
-      <c r="D190" s="2"/>
-      <c r="K190" s="2"/>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A191" s="23"/>
-      <c r="B191" s="2"/>
-      <c r="C191" s="2"/>
-      <c r="D191" s="2"/>
-      <c r="K191" s="2"/>
-    </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A192" s="23"/>
-      <c r="B192" s="2"/>
-      <c r="C192" s="2"/>
-      <c r="D192" s="2"/>
-      <c r="K192" s="2"/>
-    </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A193" s="23"/>
-      <c r="B193" s="2"/>
-      <c r="C193" s="2"/>
-      <c r="D193" s="2"/>
-      <c r="K193" s="2"/>
-    </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A194" s="23"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
-      <c r="K194" s="2"/>
-    </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A195" s="23"/>
-      <c r="B195" s="2"/>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="K195" s="2"/>
-    </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A196" s="23"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="K196" s="2"/>
-    </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A197" s="23"/>
-      <c r="B197" s="2"/>
-      <c r="C197" s="2"/>
-      <c r="D197" s="2"/>
-      <c r="K197" s="2"/>
-    </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A198" s="23"/>
-      <c r="B198" s="2"/>
-      <c r="C198" s="2"/>
-      <c r="D198" s="2"/>
-      <c r="K198" s="2"/>
-    </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A199" s="23"/>
-      <c r="B199" s="2"/>
-      <c r="C199" s="2"/>
-      <c r="D199" s="2"/>
-      <c r="K199" s="2"/>
-    </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A200" s="23">
-        <f ca="1">TODAY()</f>
-        <v>46235</v>
-      </c>
-      <c r="B200" s="2"/>
-      <c r="C200" s="2"/>
-      <c r="D200" s="2"/>
-      <c r="K200" s="24">
-        <f>Overview!U3</f>
-        <v>1125.3399999999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -18312,7 +19602,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -19480,6 +20770,1136 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B721A49-178D-43C2-AF06-42DA04A897EC}">
+  <dimension ref="A1:AA42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
+    <col min="5" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="19" width="10.7109375" customWidth="1"/>
+    <col min="20" max="24" width="8.7109375" customWidth="1"/>
+    <col min="25" max="27" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="M1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="30"/>
+      <c r="O1" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="R1" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="S1" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y1" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46363</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0</v>
+      </c>
+      <c r="F2" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="10" t="str">
+        <f>IF(J2&gt;0,J2-D2,"")</f>
+        <v/>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="Y2" s="11">
+        <f>B3</f>
+        <v>46254</v>
+      </c>
+      <c r="Z2" s="3">
+        <f>B11*-1</f>
+        <v>-122.1</v>
+      </c>
+      <c r="AA2" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="11">
+        <v>46254</v>
+      </c>
+      <c r="D3" s="11">
+        <v>46453</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5">
+        <v>2.8</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="10" t="str">
+        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="5">
+        <f>B11</f>
+        <v>122.1</v>
+      </c>
+      <c r="N3" s="5">
+        <f>G42</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="5">
+        <f>F42</f>
+        <v>11.11</v>
+      </c>
+      <c r="P3" s="5">
+        <f>H42+I42</f>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="13" t="str">
+        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
+        <v/>
+      </c>
+      <c r="R3" s="11" t="str">
+        <f>IF(M3=N3,B14,"")</f>
+        <v/>
+      </c>
+      <c r="S3" s="3" t="str">
+        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
+        <v/>
+      </c>
+      <c r="Y3" s="11">
+        <f>J2</f>
+        <v>0</v>
+      </c>
+      <c r="Z3" s="5">
+        <f>G2+H2+I2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="11">
+        <v>46260</v>
+      </c>
+      <c r="D4" s="11">
+        <v>46545</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>2.86</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y4" s="11">
+        <f t="shared" ref="Y4:Y41" si="1">J3</f>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5">
+        <f t="shared" ref="Z4:Z41" si="2">G3+H3+I3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="11">
+        <v>46617</v>
+      </c>
+      <c r="E5" s="5">
+        <v>122.1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y5" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y6" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y7" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3">
+        <v>12</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y8" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="11"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y9" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y10" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B11" s="5">
+        <v>122.1</v>
+      </c>
+      <c r="D11" s="11"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y11" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="11">
+        <v>46617</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y12" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z12" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="10">
+        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
+        <v>351</v>
+      </c>
+      <c r="D13" s="11"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y13" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="11"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y14" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z14" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="3" t="str">
+        <f>IF(M3=N3,B14-B12,"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y15" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="D16" s="7"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y16" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D17" s="7"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y17" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D18" s="7"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y18" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D19" s="7"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y19" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z19" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D20" s="7"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y20" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y21" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D22" s="7"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y22" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D23" s="7"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y23" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z23" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D24" s="7"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y24" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D25" s="7"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y25" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z25" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D26" s="7"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y26" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z26" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D27" s="7"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y27" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z27" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D28" s="7"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z28" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D29" s="7"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y29" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z29" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D30" s="7"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y30" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z30" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D31" s="7"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y31" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z31" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D32" s="7"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y32" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z32" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D33" s="7"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y33" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z33" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D34" s="7"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y34" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z34" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D35" s="7"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z35" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D36" s="7"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y36" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z36" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D37" s="7"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y37" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D38" s="7"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y38" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z38" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y39" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z39" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D40" s="7"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y40" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z40" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D41" s="7"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="Y41" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Z41" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
+      <c r="D42" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E42" s="5">
+        <f>SUM(E2:E41)</f>
+        <v>122.1</v>
+      </c>
+      <c r="F42" s="5">
+        <f t="shared" ref="F42:I42" si="3">SUM(F2:F41)</f>
+        <v>11.11</v>
+      </c>
+      <c r="G42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I42" s="5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="S1:S2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="expression" dxfId="79" priority="1">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="78" priority="2">
+      <formula>$M$3=$N$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S3">
+    <cfRule type="expression" dxfId="77" priority="3">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2">
+    <cfRule type="expression" dxfId="76" priority="4">
+      <formula>$AA$2="+"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{774FA271-9215-4369-9468-273925BE7FC4}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19571,13 +21991,21 @@
       <c r="F2" s="5">
         <v>2.19</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="10" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.19</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46265</v>
+      </c>
+      <c r="K2" s="10">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -19645,7 +22073,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -19661,11 +22089,11 @@
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -19820,7 +22248,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="5"/>
@@ -19929,7 +22357,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -20568,7 +22996,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -20609,7 +23037,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB309DC-D140-4386-90FC-0C778E67F5B1}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20701,13 +23129,21 @@
       <c r="F2" s="5">
         <v>2.68</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="10" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.68</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46265</v>
+      </c>
+      <c r="K2" s="10">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -20775,7 +23211,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -20791,11 +23227,11 @@
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
-        <v>0</v>
+        <v>46265</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -20950,7 +23386,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="5"/>
@@ -21059,7 +23495,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -21698,7 +24134,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="5"/>
@@ -21739,7 +24175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B243AB69-C22B-4D12-9872-F3C578B33FFE}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -21831,13 +24267,21 @@
       <c r="F2" s="5">
         <v>2.54</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="10" t="str">
+      <c r="G2" s="5">
+        <v>0</v>
+      </c>
+      <c r="H2" s="5">
+        <v>2.54</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="J2" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K2" s="10">
         <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v/>
+        <v>32</v>
       </c>
       <c r="M2" s="15" t="s">
         <v>68</v>
@@ -21864,7 +24308,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v>+</v>
+        <v/>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -21905,7 +24349,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -21915,17 +24359,17 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
-        <v>0</v>
+        <v>46266</v>
       </c>
       <c r="Z3" s="5">
         <f>G2+H2+I2</f>
-        <v>0</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -22080,7 +24524,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="5"/>
@@ -22189,7 +24633,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="5"/>
@@ -22828,11 +25272,11 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -22869,7 +25313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC91ED6D-15FE-46C0-B0C3-FBB1CB961A40}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23051,7 +25495,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>4.29</v>
+        <v>5.34</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -23172,13 +25616,21 @@
       <c r="F6" s="5">
         <v>1.05</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.05</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" si="0"/>
+        <v>1</v>
       </c>
       <c r="Y6" s="11">
         <f t="shared" si="1"/>
@@ -23215,11 +25667,11 @@
       </c>
       <c r="Y7" s="11">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>46266</v>
       </c>
       <c r="Z7" s="5">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
@@ -23393,7 +25845,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="D13" s="11">
         <v>46470</v>
@@ -24038,7 +26490,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="9"/>
-        <v>4.29</v>
+        <v>5.34</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="9"/>
@@ -24079,7 +26531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24230,13 +26682,21 @@
       <c r="F3" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="10" t="str">
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="11">
+        <v>46266</v>
+      </c>
+      <c r="K3" s="10">
         <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M3" s="5">
         <f>B11</f>
@@ -24252,7 +26712,7 @@
       </c>
       <c r="P3" s="5">
         <f>H42+I42</f>
-        <v>2.4</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="Q3" s="13" t="str">
         <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
@@ -24301,11 +26761,11 @@
       </c>
       <c r="Y4" s="11">
         <f t="shared" ref="Y4:Y13" si="1">J3</f>
-        <v>0</v>
+        <v>46266</v>
       </c>
       <c r="Z4" s="5">
         <f t="shared" ref="Z4:Z13" si="2">G3+H3+I3</f>
-        <v>0</v>
+        <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -24536,7 +26996,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -25175,7 +27635,7 @@
       </c>
       <c r="H42" s="5">
         <f t="shared" si="7"/>
-        <v>2.4</v>
+        <v>4.6999999999999993</v>
       </c>
       <c r="I42" s="5">
         <f t="shared" si="7"/>
@@ -25216,7 +27676,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AA42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -25349,7 +27809,7 @@
       </c>
       <c r="AA2" s="3" t="str">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
+        <v>+</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -25400,9 +27860,9 @@
         <f>IF(M3=N3,B14,"")</f>
         <v/>
       </c>
-      <c r="S3" s="3" t="str">
+      <c r="S3" s="3">
         <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y3" s="11">
         <f>J2</f>
@@ -25674,7 +28134,7 @@
       </c>
       <c r="B13" s="10">
         <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -26352,1150 +28812,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AA42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" customWidth="1"/>
-    <col min="13" max="19" width="10.7109375" customWidth="1"/>
-    <col min="20" max="24" width="8.7109375" customWidth="1"/>
-    <col min="25" max="27" width="10.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="30"/>
-      <c r="O1" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="R1" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="S1" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y1" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="Z1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA1" s="7" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" s="11">
-        <v>46142</v>
-      </c>
-      <c r="E2" s="5">
-        <v>0</v>
-      </c>
-      <c r="F2" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
-        <v>2.44</v>
-      </c>
-      <c r="I2" s="5">
-        <v>0</v>
-      </c>
-      <c r="J2" s="11">
-        <v>46142</v>
-      </c>
-      <c r="K2" s="10">
-        <f>IF(J2&gt;0,J2-D2,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="O2" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="Y2" s="11">
-        <f>B3</f>
-        <v>46028</v>
-      </c>
-      <c r="Z2" s="3">
-        <f>B11*-1</f>
-        <v>-104.1</v>
-      </c>
-      <c r="AA2" s="3" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")&gt;0,"+","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="11">
-        <v>46028</v>
-      </c>
-      <c r="D3" s="11">
-        <v>46234</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0</v>
-      </c>
-      <c r="J3" s="11">
-        <v>46234</v>
-      </c>
-      <c r="K3" s="10">
-        <f t="shared" ref="K3:K41" si="0">IF(J3&gt;0,J3-D3,"")</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="5">
-        <f>B11</f>
-        <v>104.1</v>
-      </c>
-      <c r="N3" s="5">
-        <f>G42</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="5">
-        <f>F42</f>
-        <v>8.2800000000000011</v>
-      </c>
-      <c r="P3" s="5">
-        <f>H42+I42</f>
-        <v>4.54</v>
-      </c>
-      <c r="Q3" s="13" t="str">
-        <f>IF(M3=N3,XIRR(Z2:Z41,Y2:Y41),"")</f>
-        <v/>
-      </c>
-      <c r="R3" s="11" t="str">
-        <f>IF(M3=N3,B14,"")</f>
-        <v/>
-      </c>
-      <c r="S3" s="3" t="str">
-        <f ca="1">IF(COUNTIFS(D:D,"&lt;"&amp;TODAY(),J:J,"")=0,"",TODAY()-_xlfn.MINIFS(D:D,D:D,"&lt;"&amp;TODAY(),J:J,""))</f>
-        <v/>
-      </c>
-      <c r="Y3" s="11">
-        <f>J2</f>
-        <v>46142</v>
-      </c>
-      <c r="Z3" s="5">
-        <f>G2+H2+I2</f>
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="11">
-        <v>46034</v>
-      </c>
-      <c r="D4" s="11">
-        <v>46326</v>
-      </c>
-      <c r="E4" s="5">
-        <v>0</v>
-      </c>
-      <c r="F4" s="5">
-        <v>2.1</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y4" s="11">
-        <f t="shared" ref="Y4:Y13" si="1">J3</f>
-        <v>46234</v>
-      </c>
-      <c r="Z4" s="5">
-        <f t="shared" ref="Z4:Z13" si="2">G3+H3+I3</f>
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="11">
-        <v>46398</v>
-      </c>
-      <c r="E5" s="5">
-        <v>104.1</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1.64</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y5" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z5" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y6" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z6" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y7" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z7" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3">
-        <v>12</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y8" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z8" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y9" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z9" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6">
-        <v>0.08</v>
-      </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y10" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z10" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="5">
-        <v>104.1</v>
-      </c>
-      <c r="D11" s="11"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y11" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z11" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" s="21">
-        <v>46398</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y12" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z12" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="10">
-        <f ca="1">IF(B11&lt;&gt;N3,(TODAY()-B12)*-1,"")</f>
-        <v>163</v>
-      </c>
-      <c r="D13" s="19"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y13" s="11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Z13" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="B14" s="11"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y14" s="11">
-        <f t="shared" ref="Y14" si="3">J13</f>
-        <v>0</v>
-      </c>
-      <c r="Z14" s="5">
-        <f t="shared" ref="Z14" si="4">G13+H13+I13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="B15" s="3" t="str">
-        <f>IF(M3=N3,B14-B12,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y15" s="11">
-        <f t="shared" ref="Y15:Y41" si="5">J14</f>
-        <v>0</v>
-      </c>
-      <c r="Z15" s="5">
-        <f t="shared" ref="Z15:Z41" si="6">G14+H14+I14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="D16" s="7"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y16" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z16" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D17" s="7"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y17" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z17" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D18" s="7"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y18" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z18" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D19" s="7"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y19" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z19" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D20" s="7"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y20" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z20" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D21" s="7"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y21" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z21" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D22" s="7"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y22" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z22" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D23" s="7"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y23" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z23" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D24" s="7"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y24" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z24" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D25" s="7"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y25" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z25" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D26" s="7"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y26" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z26" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D27" s="7"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y27" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z27" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D28" s="7"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y28" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z28" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D29" s="7"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y29" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z29" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D30" s="7"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y30" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z30" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D31" s="7"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y31" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z31" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D32" s="7"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y32" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z32" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D33" s="7"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="3"/>
-      <c r="K33" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y33" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z33" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D34" s="7"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y34" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z34" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D35" s="7"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="3"/>
-      <c r="K35" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y35" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z35" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D36" s="7"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y36" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z36" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D37" s="7"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y37" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z37" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D38" s="7"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y38" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z38" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D39" s="7"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="3"/>
-      <c r="K39" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y39" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z39" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D40" s="7"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y40" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z40" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D41" s="7"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="Y41" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Z41" s="5">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="4:26" x14ac:dyDescent="0.25">
-      <c r="D42" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="5">
-        <f>SUM(E2:E41)</f>
-        <v>104.1</v>
-      </c>
-      <c r="F42" s="5">
-        <f t="shared" ref="F42:I42" si="7">SUM(F2:F41)</f>
-        <v>8.2800000000000011</v>
-      </c>
-      <c r="G42" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H42" s="5">
-        <f t="shared" si="7"/>
-        <v>4.54</v>
-      </c>
-      <c r="I42" s="5">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="S1:S2"/>
-    <mergeCell ref="R1:R2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="expression" dxfId="51" priority="14">
-      <formula>$M$3=$N$3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="50" priority="15">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="S3">
-    <cfRule type="expression" dxfId="49" priority="4">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2">
-    <cfRule type="expression" dxfId="48" priority="3">
-      <formula>$AA$2="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>